--- a/6班_機能一覧.xlsx
+++ b/6班_機能一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miino\No.6-FeatureList\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BA70D6-7748-4B3C-9615-AF1F4093994E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7F28CE-8D1F-45BF-B0C2-8DA59BD1C012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,12 +85,6 @@
     <t>・各機能の概要と担当者</t>
   </si>
   <si>
-    <t>メイン機能1</t>
-  </si>
-  <si>
-    <t>トーク機能を作る（生徒同士でも話せる場をつくる）</t>
-  </si>
-  <si>
     <t>北野</t>
   </si>
   <si>
@@ -98,12 +92,6 @@
   </si>
   <si>
     <t>・例: https://docs.google.com/spreadsheets/d/1bObGDleq8ijOa44m9LaKeAwAmYdAl719a1X5Dc0GrRY/edit?usp=sharing</t>
-  </si>
-  <si>
-    <t>メイン機能2</t>
-  </si>
-  <si>
-    <t>リアクション機能をつける</t>
   </si>
   <si>
     <t>ゆゆこ</t>
@@ -143,6 +131,18 @@
   </si>
   <si>
     <t>MANABI‐BA</t>
+  </si>
+  <si>
+    <t>トーク機能(メイン)</t>
+  </si>
+  <si>
+    <t>授業ごとの内容を生徒同士でも話せる場をつくる</t>
+  </si>
+  <si>
+    <t>リアクション機能</t>
+  </si>
+  <si>
+    <t>絵文字👍・❤</t>
   </si>
 </sst>
 </file>
@@ -562,7 +562,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -770,21 +770,21 @@
     <row r="8" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -808,13 +808,13 @@
     <row r="9" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="7" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="2"/>
@@ -848,7 +848,7 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -899,10 +899,10 @@
     </row>
     <row r="12" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -910,7 +910,7 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -940,7 +940,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -998,7 +998,7 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -1028,7 +1028,7 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -1058,7 +1058,7 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -1088,7 +1088,7 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -1118,7 +1118,7 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -1148,7 +1148,7 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -28612,7 +28612,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="B12" r:id="rId1" xr:uid="{9089B003-43F8-47EB-ABAB-BAEC12074F39}"/>
+    <hyperlink ref="B12" r:id="rId1" xr:uid="{2586C0A4-A00D-4354-9837-620D3F05C6A0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/6班_機能一覧.xlsx
+++ b/6班_機能一覧.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miino\No.6-FeatureList\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miino\Downloads\No.6-FeatureList\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7F28CE-8D1F-45BF-B0C2-8DA59BD1C012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4077DC-AB49-4B75-88D3-2802062FA11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="シート1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>機能一覧表</t>
   </si>
@@ -144,12 +145,93 @@
   <si>
     <t>絵文字👍・❤</t>
   </si>
+  <si>
+    <t>役割</t>
+    <rPh sb="0" eb="2">
+      <t>ヤクワリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>担当者</t>
+    <rPh sb="0" eb="3">
+      <t>タントウシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>主な役割</t>
+    <rPh sb="0" eb="1">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヤクワリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>補足</t>
+    <rPh sb="0" eb="2">
+      <t>ホソク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プロジェクトマネージャ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技術リーダー</t>
+    <rPh sb="0" eb="2">
+      <t>ギジュツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>デザインリーダー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>テストリーダー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>にゃは</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>発表者</t>
+    <rPh sb="0" eb="3">
+      <t>ハッピョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>はまよし</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>たまい</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>きたの</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おか</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>はせ　きたの　はまよし　たまい　おか</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -184,6 +266,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="3">
@@ -273,7 +362,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -299,6 +388,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -28616,4 +28707,80 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF39FCB1-16A3-4858-AA68-8B6205556F8D}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.44140625" customWidth="1"/>
+    <col min="2" max="2" width="63" customWidth="1"/>
+    <col min="3" max="3" width="24.88671875" customWidth="1"/>
+    <col min="4" max="4" width="30.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>